--- a/p3_data_preparation/data/italy/integrate_data/df_teams.xlsx
+++ b/p3_data_preparation/data/italy/integrate_data/df_teams.xlsx
@@ -443,108 +443,108 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>lazio</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>fiorentina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>juventus</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QDdvI0zl</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sassuolo</t>
+          <t>ac milan</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>lecce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>genoa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>bologna</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>cagliari</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>QDdvI0zl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>sassuolo</t>
         </is>
       </c>
     </row>
@@ -563,36 +563,36 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>inter</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>atalanta</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>empoli</t>
         </is>
       </c>
     </row>
@@ -611,72 +611,72 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Mq05g4BP</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salernitana</t>
+          <t>verona</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>torino</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>monza</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>udinese</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>as roma</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>Mq05g4BP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>salernitana</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>reggio calabria</t>
+          <t>reggina</t>
         </is>
       </c>
     </row>
@@ -2135,432 +2135,432 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>Mc1agWrH</t>
+          <t>IsxHSx6l</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>casarano</t>
+          <t>lecco</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>0pDX5Wg6</t>
+          <t>Mc1agWrH</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>s  n  notaresco</t>
+          <t>casarano</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>WfIyojRQ</t>
+          <t>0pDX5Wg6</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>breno</t>
+          <t>s  n  notaresco</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>S8fKXrK7</t>
+          <t>WfIyojRQ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>pineto</t>
+          <t>breno</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>0zHclzCf</t>
+          <t>S8fKXrK7</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>tritium</t>
+          <t>pineto</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>6TpeXROt</t>
+          <t>0zHclzCf</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ambrosiana</t>
+          <t>tritium</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>EgYzZsf9</t>
+          <t>6TpeXROt</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>gelbison</t>
+          <t>ambrosiana</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>nD1wFLEn</t>
+          <t>EgYzZsf9</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>latte dolce</t>
+          <t>gelbison</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>z1EHJzXR</t>
+          <t>nD1wFLEn</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>lanusei calcio</t>
+          <t>latte dolce</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>jP39RxoA</t>
+          <t>z1EHJzXR</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>turris</t>
+          <t>lanusei calcio</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>Oj776UZ3</t>
+          <t>jP39RxoA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>fanfulla</t>
+          <t>turris</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>zeb1cRhK</t>
+          <t>Oj776UZ3</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ponsacco</t>
+          <t>fanfulla</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>rwQckP0s</t>
+          <t>zeb1cRhK</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>matelica</t>
+          <t>ponsacco</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bLYPmFPe</t>
+          <t>rwQckP0s</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>citta di fasano</t>
+          <t>matelica</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>Q3owK3O1</t>
+          <t>bLYPmFPe</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>rende</t>
+          <t>citta di fasano</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>YifOyQ0J</t>
+          <t>Q3owK3O1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>rezzato</t>
+          <t>rende</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>fZbXYcEq</t>
+          <t>YifOyQ0J</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>sicula leonzio</t>
+          <t>rezzato</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>Sf3F3QGc</t>
+          <t>fZbXYcEq</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>chieri</t>
+          <t>sicula leonzio</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>KC845WJ5</t>
+          <t>Sf3F3QGc</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>albalonga</t>
+          <t>chieri</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>Ee7aFeEG</t>
+          <t>KC845WJ5</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>picerno</t>
+          <t>albalonga</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>QevJunLG</t>
+          <t>Ee7aFeEG</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>monterosi</t>
+          <t>picerno</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>OOVihjFO</t>
+          <t>QevJunLG</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ciliverghe mazzano</t>
+          <t>monterosi</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>dS0uWnrT</t>
+          <t>OOVihjFO</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>pro piacenza</t>
+          <t>ciliverghe mazzano</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>S2uLYlbA</t>
+          <t>dS0uWnrT</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>seregno</t>
+          <t>pro piacenza</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>lUFr2CrF</t>
+          <t>S2uLYlbA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>maceratese</t>
+          <t>seregno</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>bLlDpBzU</t>
+          <t>lUFr2CrF</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>nerostellati frattese</t>
+          <t>maceratese</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>fetSNIR1</t>
+          <t>bLlDpBzU</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>caronnese</t>
+          <t>nerostellati frattese</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>UsH271za</t>
+          <t>fetSNIR1</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>francavilla</t>
+          <t>caronnese</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>d6FpIZHO</t>
+          <t>UsH271za</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>valdinievole montecatini</t>
+          <t>francavilla</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>EgAc8nDP</t>
+          <t>d6FpIZHO</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>tuttocuoio</t>
+          <t>valdinievole montecatini</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>Kt2rPwYb</t>
+          <t>EgAc8nDP</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>altovicentino</t>
+          <t>tuttocuoio</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>EBIGF2fE</t>
+          <t>Kt2rPwYb</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>fano</t>
+          <t>altovicentino</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>4AlHorrq</t>
+          <t>EBIGF2fE</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>poggibonsi</t>
+          <t>fano</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>OIfKN9XI</t>
+          <t>4AlHorrq</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>sestri levante</t>
+          <t>poggibonsi</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>hIOYtNOj</t>
+          <t>OIfKN9XI</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>delta porto tolle</t>
+          <t>sestri levante</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>IsxHSx6l</t>
+          <t>hIOYtNOj</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>lecco</t>
+          <t>delta porto tolle</t>
         </is>
       </c>
     </row>
